--- a/docs/oc-mensuales/gas-licuado-de-petroleo/mar-2026.xlsx
+++ b/docs/oc-mensuales/gas-licuado-de-petroleo/mar-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC mar-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC mar-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8738,7 +8738,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9886,7 +9886,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -10805,7 +10805,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10927,7 +10927,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11186,7 +11186,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -12105,7 +12105,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -12277,7 +12277,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12521,7 +12521,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -13070,7 +13070,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -13989,7 +13989,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14233,7 +14233,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14721,7 +14721,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -15697,7 +15697,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -16002,7 +16002,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -16490,7 +16490,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16734,7 +16734,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -16978,7 +16978,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -17222,7 +17222,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -17405,7 +17405,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -18442,7 +18442,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -18503,7 +18503,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -19296,7 +19296,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -19540,7 +19540,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -20089,7 +20089,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -21004,7 +21004,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -21065,7 +21065,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -23078,7 +23078,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -23505,7 +23505,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -23688,7 +23688,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -23993,7 +23993,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -24786,7 +24786,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -24847,7 +24847,7 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
@@ -25396,7 +25396,7 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -25701,7 +25701,7 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
@@ -25762,7 +25762,7 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
@@ -26006,7 +26006,7 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
@@ -26433,7 +26433,7 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
@@ -26555,7 +26555,7 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
@@ -26860,7 +26860,7 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -27226,7 +27226,7 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -27287,7 +27287,7 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
@@ -27836,7 +27836,7 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -27897,7 +27897,7 @@
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
@@ -28324,7 +28324,7 @@
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
@@ -28507,7 +28507,7 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -29300,7 +29300,7 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
@@ -29849,7 +29849,7 @@
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
@@ -30459,7 +30459,7 @@
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
@@ -30886,7 +30886,7 @@
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
@@ -31313,7 +31313,7 @@
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
@@ -31496,7 +31496,7 @@
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
@@ -31557,7 +31557,7 @@
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -31923,7 +31923,7 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -32167,7 +32167,7 @@
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
@@ -32655,7 +32655,7 @@
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
@@ -32899,7 +32899,7 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -33021,7 +33021,7 @@
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
@@ -33814,7 +33814,7 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -35095,7 +35095,7 @@
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
@@ -35461,7 +35461,7 @@
       </c>
       <c r="H574" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I574" t="inlineStr">
@@ -35522,7 +35522,7 @@
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
@@ -35827,7 +35827,7 @@
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I580" t="inlineStr">
@@ -35949,7 +35949,7 @@
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -36620,7 +36620,7 @@
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I593" t="inlineStr">
@@ -36986,7 +36986,7 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -37169,7 +37169,7 @@
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
@@ -37230,7 +37230,7 @@
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I603" t="inlineStr">
@@ -37840,7 +37840,7 @@
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I613" t="inlineStr">
@@ -38206,7 +38206,7 @@
       </c>
       <c r="H619" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I619" t="inlineStr">
@@ -38267,7 +38267,7 @@
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I620" t="inlineStr">
@@ -38572,7 +38572,7 @@
       </c>
       <c r="H625" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I625" t="inlineStr">
@@ -39121,7 +39121,7 @@
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I634" t="inlineStr">
@@ -39182,7 +39182,7 @@
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I635" t="inlineStr">
@@ -39670,7 +39670,7 @@
       </c>
       <c r="H643" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I643" t="inlineStr">
@@ -40036,7 +40036,7 @@
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I649" t="inlineStr">
@@ -40646,7 +40646,7 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -41134,7 +41134,7 @@
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I667" t="inlineStr">
@@ -41195,7 +41195,7 @@
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I668" t="inlineStr">
@@ -42171,7 +42171,7 @@
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
@@ -42354,7 +42354,7 @@
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I687" t="inlineStr">
@@ -42598,7 +42598,7 @@
       </c>
       <c r="H691" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I691" t="inlineStr">
@@ -43574,7 +43574,7 @@
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I707" t="inlineStr">
@@ -43635,7 +43635,7 @@
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I708" t="inlineStr">
@@ -44306,7 +44306,7 @@
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
@@ -44550,7 +44550,7 @@
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I723" t="inlineStr">
@@ -44672,7 +44672,7 @@
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
@@ -45160,7 +45160,7 @@
       </c>
       <c r="H733" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I733" t="inlineStr">
@@ -46014,7 +46014,7 @@
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I747" t="inlineStr">
@@ -46197,7 +46197,7 @@
       </c>
       <c r="H750" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I750" t="inlineStr">
@@ -46502,7 +46502,7 @@
       </c>
       <c r="H755" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I755" t="inlineStr">
@@ -47356,7 +47356,7 @@
       </c>
       <c r="H769" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I769" t="inlineStr">
@@ -47417,7 +47417,7 @@
       </c>
       <c r="H770" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I770" t="inlineStr">
@@ -47478,7 +47478,7 @@
       </c>
       <c r="H771" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I771" t="inlineStr">
@@ -47661,7 +47661,7 @@
       </c>
       <c r="H774" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I774" t="inlineStr">
@@ -47905,7 +47905,7 @@
       </c>
       <c r="H778" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I778" t="inlineStr">
@@ -48088,7 +48088,7 @@
       </c>
       <c r="H781" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I781" t="inlineStr">
@@ -49125,7 +49125,7 @@
       </c>
       <c r="H798" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I798" t="inlineStr">
@@ -49613,7 +49613,7 @@
       </c>
       <c r="H806" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I806" t="inlineStr">
@@ -49979,7 +49979,7 @@
       </c>
       <c r="H812" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I812" t="inlineStr">
@@ -50223,7 +50223,7 @@
       </c>
       <c r="H816" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I816" t="inlineStr">
@@ -51321,7 +51321,7 @@
       </c>
       <c r="H834" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I834" t="inlineStr">
@@ -51687,7 +51687,7 @@
       </c>
       <c r="H840" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I840" t="inlineStr">
@@ -51748,7 +51748,7 @@
       </c>
       <c r="H841" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I841" t="inlineStr">
@@ -51870,7 +51870,7 @@
       </c>
       <c r="H843" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I843" t="inlineStr">
@@ -51992,7 +51992,7 @@
       </c>
       <c r="H845" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I845" t="inlineStr">
@@ -52297,7 +52297,7 @@
       </c>
       <c r="H850" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I850" t="inlineStr">
@@ -52541,7 +52541,7 @@
       </c>
       <c r="H854" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I854" t="inlineStr">
@@ -52663,7 +52663,7 @@
       </c>
       <c r="H856" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I856" t="inlineStr">
@@ -52968,7 +52968,7 @@
       </c>
       <c r="H861" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I861" t="inlineStr">
@@ -53029,7 +53029,7 @@
       </c>
       <c r="H862" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I862" t="inlineStr">
@@ -54920,7 +54920,7 @@
       </c>
       <c r="H893" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I893" t="inlineStr">
@@ -55530,7 +55530,7 @@
       </c>
       <c r="H903" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I903" t="inlineStr">
@@ -56079,7 +56079,7 @@
       </c>
       <c r="H912" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I912" t="inlineStr">
@@ -56155,7 +56155,7 @@
       </c>
       <c r="K913" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L913" t="inlineStr">
@@ -56220,7 +56220,7 @@
       </c>
       <c r="K914" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L914" t="inlineStr">
@@ -56331,7 +56331,7 @@
       </c>
       <c r="H916" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I916" t="inlineStr">
@@ -56453,7 +56453,7 @@
       </c>
       <c r="H918" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I918" t="inlineStr">
@@ -56575,7 +56575,7 @@
       </c>
       <c r="H920" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I920" t="inlineStr">
@@ -56636,7 +56636,7 @@
       </c>
       <c r="H921" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I921" t="inlineStr">
@@ -56697,7 +56697,7 @@
       </c>
       <c r="H922" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I922" t="inlineStr">
@@ -57002,7 +57002,7 @@
       </c>
       <c r="H927" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I927" t="inlineStr">
@@ -57124,7 +57124,7 @@
       </c>
       <c r="H929" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I929" t="inlineStr">
@@ -57139,7 +57139,7 @@
       </c>
       <c r="K929" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L929" t="inlineStr">
@@ -57189,7 +57189,7 @@
       </c>
       <c r="H930" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I930" t="inlineStr">
@@ -57311,7 +57311,7 @@
       </c>
       <c r="H932" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I932" t="inlineStr">
@@ -57433,7 +57433,7 @@
       </c>
       <c r="H934" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I934" t="inlineStr">
@@ -57616,7 +57616,7 @@
       </c>
       <c r="H937" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I937" t="inlineStr">
@@ -57677,7 +57677,7 @@
       </c>
       <c r="H938" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I938" t="inlineStr">
@@ -57738,7 +57738,7 @@
       </c>
       <c r="H939" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I939" t="inlineStr">
@@ -57799,7 +57799,7 @@
       </c>
       <c r="H940" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I940" t="inlineStr">
@@ -57921,7 +57921,7 @@
       </c>
       <c r="H942" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I942" t="inlineStr">
@@ -58470,7 +58470,7 @@
       </c>
       <c r="H951" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I951" t="inlineStr">
@@ -58607,7 +58607,7 @@
       </c>
       <c r="K953" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L953" t="inlineStr">
@@ -58657,7 +58657,7 @@
       </c>
       <c r="H954" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I954" t="inlineStr">
@@ -58962,7 +58962,7 @@
       </c>
       <c r="H959" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I959" t="inlineStr">
@@ -59267,7 +59267,7 @@
       </c>
       <c r="H964" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I964" t="inlineStr">
@@ -59938,7 +59938,7 @@
       </c>
       <c r="H975" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I975" t="inlineStr">
@@ -59999,7 +59999,7 @@
       </c>
       <c r="H976" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I976" t="inlineStr">
@@ -60182,7 +60182,7 @@
       </c>
       <c r="H979" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I979" t="inlineStr">
@@ -60548,7 +60548,7 @@
       </c>
       <c r="H985" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I985" t="inlineStr">
@@ -61036,7 +61036,7 @@
       </c>
       <c r="H993" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I993" t="inlineStr">
@@ -61341,7 +61341,7 @@
       </c>
       <c r="H998" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I998" t="inlineStr">
@@ -61463,7 +61463,7 @@
       </c>
       <c r="H1000" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1000" t="inlineStr">
@@ -61524,7 +61524,7 @@
       </c>
       <c r="H1001" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1001" t="inlineStr">
@@ -61585,7 +61585,7 @@
       </c>
       <c r="H1002" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1002" t="inlineStr">
@@ -61707,7 +61707,7 @@
       </c>
       <c r="H1004" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1004" t="inlineStr">
@@ -61768,7 +61768,7 @@
       </c>
       <c r="H1005" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1005" t="inlineStr">
@@ -61951,7 +61951,7 @@
       </c>
       <c r="H1008" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1008" t="inlineStr">
@@ -62256,7 +62256,7 @@
       </c>
       <c r="H1013" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1013" t="inlineStr">
@@ -62317,7 +62317,7 @@
       </c>
       <c r="H1014" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1014" t="inlineStr">
@@ -62439,7 +62439,7 @@
       </c>
       <c r="H1016" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1016" t="inlineStr">
@@ -62561,7 +62561,7 @@
       </c>
       <c r="H1018" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1018" t="inlineStr">
@@ -62622,7 +62622,7 @@
       </c>
       <c r="H1019" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1019" t="inlineStr">
@@ -62683,7 +62683,7 @@
       </c>
       <c r="H1020" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1020" t="inlineStr">
@@ -62805,7 +62805,7 @@
       </c>
       <c r="H1022" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1022" t="inlineStr">
@@ -63232,7 +63232,7 @@
       </c>
       <c r="H1029" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1029" t="inlineStr">
@@ -63598,7 +63598,7 @@
       </c>
       <c r="H1035" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1035" t="inlineStr">
@@ -63659,7 +63659,7 @@
       </c>
       <c r="H1036" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1036" t="inlineStr">
@@ -63781,7 +63781,7 @@
       </c>
       <c r="H1038" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1038" t="inlineStr">
@@ -64513,7 +64513,7 @@
       </c>
       <c r="H1050" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1050" t="inlineStr">
@@ -64574,7 +64574,7 @@
       </c>
       <c r="H1051" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I1051" t="inlineStr">
@@ -64818,7 +64818,7 @@
       </c>
       <c r="H1055" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1055" t="inlineStr">
@@ -65245,7 +65245,7 @@
       </c>
       <c r="H1062" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I1062" t="inlineStr">
@@ -65306,7 +65306,7 @@
       </c>
       <c r="H1063" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1063" t="inlineStr">
@@ -65794,7 +65794,7 @@
       </c>
       <c r="H1071" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1071" t="inlineStr">
@@ -66099,7 +66099,7 @@
       </c>
       <c r="H1076" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1076" t="inlineStr">
@@ -66221,7 +66221,7 @@
       </c>
       <c r="H1078" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1078" t="inlineStr">
@@ -66465,7 +66465,7 @@
       </c>
       <c r="H1082" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1082" t="inlineStr">
@@ -66648,7 +66648,7 @@
       </c>
       <c r="H1085" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1085" t="inlineStr">
@@ -67441,7 +67441,7 @@
       </c>
       <c r="H1098" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1098" t="inlineStr">
@@ -67807,7 +67807,7 @@
       </c>
       <c r="H1104" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1104" t="inlineStr">
@@ -68356,7 +68356,7 @@
       </c>
       <c r="H1113" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1113" t="inlineStr">
@@ -68600,7 +68600,7 @@
       </c>
       <c r="H1117" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1117" t="inlineStr">
@@ -68966,7 +68966,7 @@
       </c>
       <c r="H1123" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1123" t="inlineStr">
@@ -69332,7 +69332,7 @@
       </c>
       <c r="H1129" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1129" t="inlineStr">
@@ -69698,7 +69698,7 @@
       </c>
       <c r="H1135" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1135" t="inlineStr">
@@ -69759,7 +69759,7 @@
       </c>
       <c r="H1136" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1136" t="inlineStr">
@@ -70674,7 +70674,7 @@
       </c>
       <c r="H1151" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1151" t="inlineStr">
@@ -70979,7 +70979,7 @@
       </c>
       <c r="H1156" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1156" t="inlineStr">
@@ -71711,7 +71711,7 @@
       </c>
       <c r="H1168" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1168" t="inlineStr">
@@ -72138,7 +72138,7 @@
       </c>
       <c r="H1175" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1175" t="inlineStr">
@@ -72199,7 +72199,7 @@
       </c>
       <c r="H1176" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1176" t="inlineStr">
@@ -72992,7 +72992,7 @@
       </c>
       <c r="H1189" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1189" t="inlineStr">
@@ -73236,7 +73236,7 @@
       </c>
       <c r="H1193" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1193" t="inlineStr">
@@ -73907,7 +73907,7 @@
       </c>
       <c r="H1204" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1204" t="inlineStr">
@@ -74456,7 +74456,7 @@
       </c>
       <c r="H1213" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1213" t="inlineStr">
@@ -74944,7 +74944,7 @@
       </c>
       <c r="H1221" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1221" t="inlineStr">
@@ -75005,7 +75005,7 @@
       </c>
       <c r="H1222" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1222" t="inlineStr">
@@ -75066,7 +75066,7 @@
       </c>
       <c r="H1223" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I1223" t="inlineStr">
@@ -75432,7 +75432,7 @@
       </c>
       <c r="H1229" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1229" t="inlineStr">
@@ -76103,7 +76103,7 @@
       </c>
       <c r="H1240" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1240" t="inlineStr">
@@ -76164,7 +76164,7 @@
       </c>
       <c r="H1241" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1241" t="inlineStr">
@@ -76835,7 +76835,7 @@
       </c>
       <c r="H1252" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1252" t="inlineStr">
@@ -77506,7 +77506,7 @@
       </c>
       <c r="H1263" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1263" t="inlineStr">
@@ -77567,7 +77567,7 @@
       </c>
       <c r="H1264" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1264" t="inlineStr">
@@ -77689,7 +77689,7 @@
       </c>
       <c r="H1266" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I1266" t="inlineStr">
@@ -77872,7 +77872,7 @@
       </c>
       <c r="H1269" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1269" t="inlineStr">
@@ -77933,7 +77933,7 @@
       </c>
       <c r="H1270" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1270" t="inlineStr">
@@ -78055,7 +78055,7 @@
       </c>
       <c r="H1272" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1272" t="inlineStr">
@@ -78543,7 +78543,7 @@
       </c>
       <c r="H1280" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1280" t="inlineStr">
@@ -78665,7 +78665,7 @@
       </c>
       <c r="H1282" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I1282" t="inlineStr">
@@ -78726,7 +78726,7 @@
       </c>
       <c r="H1283" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I1283" t="inlineStr">
@@ -78909,7 +78909,7 @@
       </c>
       <c r="H1286" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1286" t="inlineStr">
@@ -78970,7 +78970,7 @@
       </c>
       <c r="H1287" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1287" t="inlineStr">
@@ -79031,7 +79031,7 @@
       </c>
       <c r="H1288" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1288" t="inlineStr">
@@ -79458,7 +79458,7 @@
       </c>
       <c r="H1295" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1295" t="inlineStr">
@@ -79641,7 +79641,7 @@
       </c>
       <c r="H1298" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1298" t="inlineStr">
@@ -80190,7 +80190,7 @@
       </c>
       <c r="H1307" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1307" t="inlineStr">
@@ -80617,7 +80617,7 @@
       </c>
       <c r="H1314" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1314" t="inlineStr">
@@ -80678,7 +80678,7 @@
       </c>
       <c r="H1315" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1315" t="inlineStr">
@@ -80739,7 +80739,7 @@
       </c>
       <c r="H1316" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1316" t="inlineStr">
@@ -80861,7 +80861,7 @@
       </c>
       <c r="H1318" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1318" t="inlineStr">
@@ -80983,7 +80983,7 @@
       </c>
       <c r="H1320" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1320" t="inlineStr">
@@ -81166,7 +81166,7 @@
       </c>
       <c r="H1323" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1323" t="inlineStr">
@@ -82020,7 +82020,7 @@
       </c>
       <c r="H1337" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I1337" t="inlineStr">
@@ -82142,7 +82142,7 @@
       </c>
       <c r="H1339" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I1339" t="inlineStr">
@@ -82508,7 +82508,7 @@
       </c>
       <c r="H1345" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1345" t="inlineStr">
@@ -82630,7 +82630,7 @@
       </c>
       <c r="H1347" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1347" t="inlineStr">
@@ -82752,7 +82752,7 @@
       </c>
       <c r="H1349" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I1349" t="inlineStr">
@@ -82813,7 +82813,7 @@
       </c>
       <c r="H1350" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1350" t="inlineStr">
@@ -83423,7 +83423,7 @@
       </c>
       <c r="H1360" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1360" t="inlineStr">
@@ -83972,7 +83972,7 @@
       </c>
       <c r="H1369" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I1369" t="inlineStr">
@@ -84887,7 +84887,7 @@
       </c>
       <c r="H1384" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1384" t="inlineStr">
@@ -85070,7 +85070,7 @@
       </c>
       <c r="H1387" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1387" t="inlineStr">
@@ -85680,7 +85680,7 @@
       </c>
       <c r="H1397" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1397" t="inlineStr">
@@ -86046,7 +86046,7 @@
       </c>
       <c r="H1403" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1403" t="inlineStr">
@@ -86351,7 +86351,7 @@
       </c>
       <c r="H1408" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1408" t="inlineStr">
@@ -86473,7 +86473,7 @@
       </c>
       <c r="H1410" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1410" t="inlineStr">
@@ -86839,7 +86839,7 @@
       </c>
       <c r="H1416" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1416" t="inlineStr">
@@ -87144,7 +87144,7 @@
       </c>
       <c r="H1421" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1421" t="inlineStr">
@@ -87266,7 +87266,7 @@
       </c>
       <c r="H1423" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1423" t="inlineStr">
@@ -87876,7 +87876,7 @@
       </c>
       <c r="H1433" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1433" t="inlineStr">
@@ -88059,7 +88059,7 @@
       </c>
       <c r="H1436" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I1436" t="inlineStr">
@@ -88303,7 +88303,7 @@
       </c>
       <c r="H1440" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1440" t="inlineStr">
@@ -88547,7 +88547,7 @@
       </c>
       <c r="H1444" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1444" t="inlineStr">
@@ -88669,7 +88669,7 @@
       </c>
       <c r="H1446" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1446" t="inlineStr">
@@ -89645,7 +89645,7 @@
       </c>
       <c r="H1462" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1462" t="inlineStr">
@@ -89828,7 +89828,7 @@
       </c>
       <c r="H1465" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I1465" t="inlineStr">
@@ -90133,7 +90133,7 @@
       </c>
       <c r="H1470" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1470" t="inlineStr">
@@ -90194,7 +90194,7 @@
       </c>
       <c r="H1471" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1471" t="inlineStr">
@@ -90316,7 +90316,7 @@
       </c>
       <c r="H1473" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1473" t="inlineStr">
@@ -90499,7 +90499,7 @@
       </c>
       <c r="H1476" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1476" t="inlineStr">
@@ -90621,7 +90621,7 @@
       </c>
       <c r="H1478" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I1478" t="inlineStr">
@@ -90865,7 +90865,7 @@
       </c>
       <c r="H1482" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1482" t="inlineStr">
@@ -90926,7 +90926,7 @@
       </c>
       <c r="H1483" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1483" t="inlineStr">
@@ -91048,7 +91048,7 @@
       </c>
       <c r="H1485" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1485" t="inlineStr">
@@ -91414,7 +91414,7 @@
       </c>
       <c r="H1491" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1491" t="inlineStr">
@@ -92024,7 +92024,7 @@
       </c>
       <c r="H1501" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1501" t="inlineStr">
@@ -92878,7 +92878,7 @@
       </c>
       <c r="H1515" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1515" t="inlineStr">
@@ -92939,7 +92939,7 @@
       </c>
       <c r="H1516" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1516" t="inlineStr">
@@ -93488,7 +93488,7 @@
       </c>
       <c r="H1525" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1525" t="inlineStr">
@@ -93610,7 +93610,7 @@
       </c>
       <c r="H1527" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1527" t="inlineStr">
@@ -93732,7 +93732,7 @@
       </c>
       <c r="H1529" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1529" t="inlineStr">
@@ -95074,7 +95074,7 @@
       </c>
       <c r="H1551" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I1551" t="inlineStr">
@@ -95257,7 +95257,7 @@
       </c>
       <c r="H1554" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I1554" t="inlineStr">
